--- a/Generate Files/BOM/243-436_PCB-Support-STM32F407.xlsx
+++ b/Generate Files/BOM/243-436_PCB-Support-STM32F407.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lecegeplimoilou-my.sharepoint.com/personal/kevin_cotton_cegeplimoilou_ca/Documents/_Cours-TGE/243-436 - Developpement de produits 4 - Dessins et Certifications/kit/243-436-PCB-Support-STM32F407/Generate Files/BOM/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lecegeplimoilou-my.sharepoint.com/personal/kevin_cotton_cegeplimoilou_ca/Documents/_Cours-TGE/243-436-Dev-Prod4-Certifications/kit/243-436-PCB-Support-STM32F407/Generate Files/BOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{00B78569-DFB2-494C-B400-8F2A881F672F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F5F8C2CF-F05C-4C22-B06F-88959762D001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AE7E1D0A-48FF-4304-A3E1-8F1D42DADE20}"/>
+    <workbookView xWindow="516" yWindow="660" windowWidth="20772" windowHeight="11580" xr2:uid="{FDB7F961-E6FF-49A7-9223-DD31578ADDCC}"/>
   </bookViews>
   <sheets>
     <sheet name="243-436_PCB-Support-STM32F407" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="181">
   <si>
     <t>LibRef</t>
   </si>
@@ -278,6 +278,30 @@
     <t>S9201-ND</t>
   </si>
   <si>
+    <t>CONN-USB-C-16POS</t>
+  </si>
+  <si>
+    <t>USB4085-GF-A</t>
+  </si>
+  <si>
+    <t>P6</t>
+  </si>
+  <si>
+    <t>CONN RCPT USB2.0 TYPE C RA - TH</t>
+  </si>
+  <si>
+    <t>? (R13-B182)</t>
+  </si>
+  <si>
+    <t>Global Connector Technology</t>
+  </si>
+  <si>
+    <t>C7095263</t>
+  </si>
+  <si>
+    <t>2073-USB4085-GF-ACT-ND</t>
+  </si>
+  <si>
     <t>CONN-100MIL-SKT-01X06</t>
   </si>
   <si>
@@ -293,19 +317,19 @@
     <t>C7499326</t>
   </si>
   <si>
-    <t>CONN-100MIL-SKT-01X08</t>
-  </si>
-  <si>
-    <t>ZX-PM2.54-1-8PY</t>
-  </si>
-  <si>
-    <t>P14A, P14B, P15A, P15B</t>
-  </si>
-  <si>
-    <t>CONN SOCKET 8pos 100mils</t>
-  </si>
-  <si>
-    <t>C7499328</t>
+    <t>CONN-5MM-3POS-TERM-BLOCK</t>
+  </si>
+  <si>
+    <t>ZX-DG28V-5.0-3P</t>
+  </si>
+  <si>
+    <t>P12</t>
+  </si>
+  <si>
+    <t>CONN TERM BLOCK 3POS 5mm pitch</t>
+  </si>
+  <si>
+    <t>CONWECO0003</t>
   </si>
   <si>
     <t>CONN-100MIL-SKT-01X20</t>
@@ -314,7 +338,7 @@
     <t>ESQ-120-14-G-S</t>
   </si>
   <si>
-    <t>P16, P17</t>
+    <t>P17</t>
   </si>
   <si>
     <t>CONN SOCKET 20POS 2.54MM</t>
@@ -338,7 +362,7 @@
     <t>Res 0R 0402</t>
   </si>
   <si>
-    <t>R3, R4, R7, R8, R9, R10, R11</t>
+    <t>R3, R4, R7, R8, R10, R11</t>
   </si>
   <si>
     <t>Resistor type 1</t>
@@ -359,7 +383,7 @@
     <t>Res 5k1 1% 0402</t>
   </si>
   <si>
-    <t>R12, R13</t>
+    <t>R9, R12, R13</t>
   </si>
   <si>
     <t>Panasonic</t>
@@ -377,7 +401,7 @@
     <t>Res 10k 1% 0402</t>
   </si>
   <si>
-    <t>R15, R19</t>
+    <t>R15, R19, R21</t>
   </si>
   <si>
     <t>Vishay</t>
@@ -953,8 +977,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3054BA9-16F5-4650-98D7-3EB44FAF2F9D}">
-  <dimension ref="A1:O25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C937924-9453-4875-B3B8-73C51EE58F9F}">
+  <dimension ref="A1:O26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31.21875" customWidth="1"/>
@@ -1390,7 +1414,7 @@
         <v>80</v>
       </c>
       <c r="C11" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>81</v>
@@ -1400,13 +1424,11 @@
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>42</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="H11" s="1"/>
       <c r="I11" s="2" t="s">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>80</v>
@@ -1415,13 +1437,13 @@
         <v>22</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>52</v>
@@ -1429,19 +1451,19 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C12" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="2" t="s">
@@ -1454,13 +1476,13 @@
         <v>57</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>22</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="M12" s="2" t="s">
         <v>42</v>
@@ -1474,45 +1496,39 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C13" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>94</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="H13" s="1"/>
       <c r="I13" s="2" t="s">
         <v>57</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>22</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>42</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
       <c r="O13" s="2" t="s">
         <v>52</v>
       </c>
@@ -1525,7 +1541,7 @@
         <v>98</v>
       </c>
       <c r="C14" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>99</v>
@@ -1534,56 +1550,60 @@
         <v>100</v>
       </c>
       <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
+      <c r="G14" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>102</v>
+      </c>
       <c r="I14" s="2" t="s">
-        <v>101</v>
+        <v>57</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>22</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
       <c r="O14" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C15" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>22</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
@@ -1593,34 +1613,34 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C16" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
@@ -1630,36 +1650,34 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C17" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>119</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="2" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
@@ -1669,34 +1687,36 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C18" s="1">
         <v>1</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="F18" s="1"/>
+        <v>108</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>127</v>
+      </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="2" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>22</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
@@ -1706,73 +1726,67 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C19" s="1">
         <v>1</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>130</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="2" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>22</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>133</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
       <c r="O19" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C20" s="1">
         <v>1</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="F20" s="1"/>
-      <c r="G20" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>138</v>
       </c>
+      <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="J20" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>22</v>
@@ -1780,89 +1794,91 @@
       <c r="L20" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
+      <c r="M20" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>141</v>
+      </c>
       <c r="O20" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C21" s="1">
         <v>1</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
+      <c r="G21" s="2" t="s">
+        <v>146</v>
+      </c>
       <c r="H21" s="1"/>
       <c r="I21" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>22</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="N21" s="2" t="s">
-        <v>147</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
       <c r="O21" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C22" s="1">
         <v>1</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>22</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>24</v>
@@ -1870,75 +1886,79 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C23" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="J23" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="F23" s="1"/>
-      <c r="G23" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>156</v>
-      </c>
       <c r="K23" s="2" t="s">
         <v>22</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
+        <v>161</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>162</v>
+      </c>
       <c r="O23" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C24" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
+      <c r="G24" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="I24" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="J24" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="J24" s="2" t="s">
-        <v>161</v>
-      </c>
       <c r="K24" s="2" t="s">
         <v>22</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
@@ -1948,42 +1968,79 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C25" s="1">
         <v>1</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>22</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="N25" s="2" t="s">
-        <v>172</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
       <c r="O25" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C26" s="1">
+        <v>1</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="O26" s="2" t="s">
         <v>52</v>
       </c>
     </row>

--- a/Generate Files/BOM/243-436_PCB-Support-STM32F407.xlsx
+++ b/Generate Files/BOM/243-436_PCB-Support-STM32F407.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lecegeplimoilou-my.sharepoint.com/personal/kevin_cotton_cegeplimoilou_ca/Documents/_Cours-TGE/243-436-Dev-Prod4-Certifications/kit/243-436-PCB-Support-STM32F407/Generate Files/BOM/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lecegeplimoilou-my.sharepoint.com/personal/kevin_cotton_cegeplimoilou_ca/Documents/_Cours-TGE/243-436-Dev-Prod4-Certifications/laboratoires/Labo1-Kit-Developpement-STM32/243-436-PCB-Support-STM32F407/Generate Files/BOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F5F8C2CF-F05C-4C22-B06F-88959762D001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{F5F8C2CF-F05C-4C22-B06F-88959762D001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D13B841-24F7-4ECC-B6FF-F7F992A83DBD}"/>
   <bookViews>
-    <workbookView xWindow="516" yWindow="660" windowWidth="20772" windowHeight="11580" xr2:uid="{FDB7F961-E6FF-49A7-9223-DD31578ADDCC}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="20112" windowHeight="12048" xr2:uid="{FDB7F961-E6FF-49A7-9223-DD31578ADDCC}"/>
   </bookViews>
   <sheets>
     <sheet name="243-436_PCB-Support-STM32F407" sheetId="1" r:id="rId1"/>
@@ -587,7 +587,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -649,7 +649,9 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{5597E743-E45E-48C9-BCDA-53213608DDC2}"/>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>

--- a/Generate Files/BOM/243-436_PCB-Support-STM32F407.xlsx
+++ b/Generate Files/BOM/243-436_PCB-Support-STM32F407.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lecegeplimoilou-my.sharepoint.com/personal/kevin_cotton_cegeplimoilou_ca/Documents/_Cours-TGE/243-436-Dev-Prod4-Certifications/laboratoires/Labo1-Kit-Developpement-STM32/243-436-PCB-Support-STM32F407/Generate Files/BOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{F5F8C2CF-F05C-4C22-B06F-88959762D001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D13B841-24F7-4ECC-B6FF-F7F992A83DBD}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E556556E-FEDB-4E74-A729-C2F99570CC24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="20112" windowHeight="12048" xr2:uid="{FDB7F961-E6FF-49A7-9223-DD31578ADDCC}"/>
+    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8880" xr2:uid="{898CD67B-8DE6-472D-ACF8-2736EC8F45DD}"/>
   </bookViews>
   <sheets>
     <sheet name="243-436_PCB-Support-STM32F407" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="217">
   <si>
     <t>LibRef</t>
   </si>
@@ -92,7 +92,7 @@
     <t>Cap 4.7uF 0805</t>
   </si>
   <si>
-    <t>C1, C5, C8, C10, C12, C14, C16A, C16B, C17A, C17B, C18, C23, C24, C25, C27</t>
+    <t>C1, C5, C7, C12, C14, C16A, C16B, C17A, C17B, C18, C19, C20, C21, C25</t>
   </si>
   <si>
     <t>Capacitor type 1</t>
@@ -122,7 +122,7 @@
     <t>Cap 100nF 0402</t>
   </si>
   <si>
-    <t>C2, C3, C6, C9, C11, C13, C15, C19, C20, C21, C22, C26</t>
+    <t>C2, C3, C6, C8, C11, C13, C15, C22, C23A, C23B, C24A, C24B</t>
   </si>
   <si>
     <t>KCOND01SM</t>
@@ -134,16 +134,34 @@
     <t>C2167491</t>
   </si>
   <si>
-    <t>CAP004</t>
-  </si>
-  <si>
-    <t>Cap 10uF 0805</t>
-  </si>
-  <si>
-    <t>C4, C7</t>
-  </si>
-  <si>
-    <t>KCOND03SM</t>
+    <t>CAP005</t>
+  </si>
+  <si>
+    <t>Cap 100uF 1206</t>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t>KCOND04SM</t>
+  </si>
+  <si>
+    <t>Murata</t>
+  </si>
+  <si>
+    <t>GRM31CR61A107MEA8L</t>
+  </si>
+  <si>
+    <t>C883598</t>
+  </si>
+  <si>
+    <t>CAP020</t>
+  </si>
+  <si>
+    <t>CAP CER 10uF 25V X5R 0805</t>
+  </si>
+  <si>
+    <t>C9, C10</t>
   </si>
   <si>
     <t>Samsung</t>
@@ -206,7 +224,7 @@
     <t>61300211121</t>
   </si>
   <si>
-    <t>J4</t>
+    <t>J2</t>
   </si>
   <si>
     <t>CONN HEADER 2POS 100MIL</t>
@@ -221,6 +239,30 @@
     <t>C7501260</t>
   </si>
   <si>
+    <t>IND001</t>
+  </si>
+  <si>
+    <t>Ind 1UH 2.75A 51mOHM SMD</t>
+  </si>
+  <si>
+    <t>L1</t>
+  </si>
+  <si>
+    <t>Inductor type 1</t>
+  </si>
+  <si>
+    <t>KPTSO09</t>
+  </si>
+  <si>
+    <t>Murata Electronics</t>
+  </si>
+  <si>
+    <t>LQH3NPN1R0MMEL</t>
+  </si>
+  <si>
+    <t>C703777</t>
+  </si>
+  <si>
     <t>CONN-100MIL-SKT-01X06_RA</t>
   </si>
   <si>
@@ -302,13 +344,31 @@
     <t>2073-USB4085-GF-ACT-ND</t>
   </si>
   <si>
+    <t>CONN-5MM-2POS-TERM-BLOCK</t>
+  </si>
+  <si>
+    <t>ZX-DG28V-5.0-2P</t>
+  </si>
+  <si>
+    <t>P7</t>
+  </si>
+  <si>
+    <t>CONN TERM BLOCK 2POS 5mm pitch</t>
+  </si>
+  <si>
+    <t>CONWECO0002</t>
+  </si>
+  <si>
+    <t>C49022995</t>
+  </si>
+  <si>
     <t>CONN-100MIL-SKT-01X06</t>
   </si>
   <si>
     <t>ZX-PM2.54-1-6PY</t>
   </si>
   <si>
-    <t>P7, P8, P9, P10, P11</t>
+    <t>P9, P10, P11, P12, P13</t>
   </si>
   <si>
     <t>CONN SOCKET 6pos 100mils</t>
@@ -323,7 +383,7 @@
     <t>ZX-DG28V-5.0-3P</t>
   </si>
   <si>
-    <t>P12</t>
+    <t>P14</t>
   </si>
   <si>
     <t>CONN TERM BLOCK 3POS 5mm pitch</t>
@@ -332,13 +392,28 @@
     <t>CONWECO0003</t>
   </si>
   <si>
+    <t>CONN-100MIL-SKT-01X08</t>
+  </si>
+  <si>
+    <t>ZX-PM2.54-1-8PY</t>
+  </si>
+  <si>
+    <t>P14A, P14B, P15A, P15B</t>
+  </si>
+  <si>
+    <t>CONN SOCKET 8pos 100mils</t>
+  </si>
+  <si>
+    <t>C7499328</t>
+  </si>
+  <si>
     <t>CONN-100MIL-SKT-01X20</t>
   </si>
   <si>
     <t>ESQ-120-14-G-S</t>
   </si>
   <si>
-    <t>P17</t>
+    <t>P15</t>
   </si>
   <si>
     <t>CONN SOCKET 20POS 2.54MM</t>
@@ -362,7 +437,7 @@
     <t>Res 0R 0402</t>
   </si>
   <si>
-    <t>R3, R4, R7, R8, R10, R11</t>
+    <t>R3, R4, R8, R10, R11, R12</t>
   </si>
   <si>
     <t>Resistor type 1</t>
@@ -383,7 +458,7 @@
     <t>Res 5k1 1% 0402</t>
   </si>
   <si>
-    <t>R9, R12, R13</t>
+    <t>R7, R13, R14</t>
   </si>
   <si>
     <t>Panasonic</t>
@@ -401,7 +476,7 @@
     <t>Res 10k 1% 0402</t>
   </si>
   <si>
-    <t>R15, R19, R21</t>
+    <t>R9, R18, R19, R21</t>
   </si>
   <si>
     <t>Vishay</t>
@@ -413,13 +488,70 @@
     <t>541-10.0KLCT-ND</t>
   </si>
   <si>
+    <t>RES011</t>
+  </si>
+  <si>
+    <t>Res 91k 1% 0402</t>
+  </si>
+  <si>
+    <t>R16</t>
+  </si>
+  <si>
+    <t>RES91KSM</t>
+  </si>
+  <si>
+    <t>RC0402FR-0791KL</t>
+  </si>
+  <si>
+    <t>C327323</t>
+  </si>
+  <si>
+    <t>RES012</t>
+  </si>
+  <si>
+    <t>Res 511k 1% 0402</t>
+  </si>
+  <si>
+    <t>R17</t>
+  </si>
+  <si>
+    <t>RES511KSM</t>
+  </si>
+  <si>
+    <t>RC0402FR-07511KL</t>
+  </si>
+  <si>
+    <t>C163461</t>
+  </si>
+  <si>
+    <t>RES014</t>
+  </si>
+  <si>
+    <t>Res 120R 1206</t>
+  </si>
+  <si>
+    <t>R20</t>
+  </si>
+  <si>
+    <t>RESI0043SMT</t>
+  </si>
+  <si>
+    <t>RC1206FR-07120RL</t>
+  </si>
+  <si>
+    <t>C114928</t>
+  </si>
+  <si>
+    <t>P120ECT-ND</t>
+  </si>
+  <si>
     <t>RES020</t>
   </si>
   <si>
     <t>Res 20R 1206</t>
   </si>
   <si>
-    <t>R16</t>
+    <t>R22</t>
   </si>
   <si>
     <t>RESI00020SMT</t>
@@ -437,7 +569,7 @@
     <t>Res 49k9 1% 0402</t>
   </si>
   <si>
-    <t>R17</t>
+    <t>R23</t>
   </si>
   <si>
     <t>RC0402FR-0749k9L</t>
@@ -446,27 +578,6 @@
     <t>C137969</t>
   </si>
   <si>
-    <t>RES014</t>
-  </si>
-  <si>
-    <t>Res 120R 1206</t>
-  </si>
-  <si>
-    <t>R20</t>
-  </si>
-  <si>
-    <t>RESI0043SMT</t>
-  </si>
-  <si>
-    <t>RC1206FR-07120RL</t>
-  </si>
-  <si>
-    <t>C114928</t>
-  </si>
-  <si>
-    <t>P120ECT-ND</t>
-  </si>
-  <si>
     <t>U_CH340X</t>
   </si>
   <si>
@@ -509,25 +620,40 @@
     <t>296-40696-1-ND</t>
   </si>
   <si>
-    <t>U_AMS1117-3.3</t>
-  </si>
-  <si>
-    <t>AMS1117-3.3</t>
+    <t>U_TPS631000DRLR</t>
+  </si>
+  <si>
+    <t>TPS631000DRLR</t>
   </si>
   <si>
     <t>U3</t>
   </si>
   <si>
-    <t>LDO Voltage Regulators 1A, 3.3V</t>
-  </si>
-  <si>
-    <t>UMW</t>
-  </si>
-  <si>
-    <t>C347222</t>
-  </si>
-  <si>
-    <t>C6186</t>
+    <t>buck-boost converter 1.5-A output current,</t>
+  </si>
+  <si>
+    <t>C5219190</t>
+  </si>
+  <si>
+    <t>296-TPS631000DRLRCT-ND</t>
+  </si>
+  <si>
+    <t>U_SN65HVD230DR</t>
+  </si>
+  <si>
+    <t>SN65HVD230DR</t>
+  </si>
+  <si>
+    <t>U4</t>
+  </si>
+  <si>
+    <t>IC TRANSCEIVER HALF 1/1 8SOIC</t>
+  </si>
+  <si>
+    <t>TI</t>
+  </si>
+  <si>
+    <t>C12084</t>
   </si>
   <si>
     <t>U_TXB0108PWR</t>
@@ -536,31 +662,13 @@
     <t>TXB0108PWR</t>
   </si>
   <si>
-    <t>U4, U5</t>
+    <t>U5A, U5B</t>
   </si>
   <si>
     <t>IC 8-Bit Bidirectional Voltage-Level Translator with Auto-Direction Sensing 20-Pin TSSOP (PW)</t>
   </si>
   <si>
     <t>C53406</t>
-  </si>
-  <si>
-    <t>U_SN65HVD230DR</t>
-  </si>
-  <si>
-    <t>SN65HVD230DR</t>
-  </si>
-  <si>
-    <t>U6</t>
-  </si>
-  <si>
-    <t>IC TRANSCEIVER HALF 1/1 8SOIC</t>
-  </si>
-  <si>
-    <t>TI</t>
-  </si>
-  <si>
-    <t>C12084</t>
   </si>
   <si>
     <t>RP-POT10K-MULTI-TURN-TOP-TH</t>
@@ -587,7 +695,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -649,9 +757,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{5597E743-E45E-48C9-BCDA-53213608DDC2}"/>
-  </tableStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -979,8 +1085,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C937924-9453-4875-B3B8-73C51EE58F9F}">
-  <dimension ref="A1:O26"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED8784F8-9DF7-4BCD-8ABB-BCA9217864F8}">
+  <dimension ref="A1:O32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31.21875" customWidth="1"/>
@@ -1049,7 +1155,7 @@
         <v>16</v>
       </c>
       <c r="C2" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>17</v>
@@ -1127,7 +1233,7 @@
         <v>32</v>
       </c>
       <c r="C4" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>33</v>
@@ -1166,138 +1272,138 @@
         <v>39</v>
       </c>
       <c r="C5" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>40</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I5" s="2" t="s">
+      <c r="K5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L5" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="J5" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>42</v>
-      </c>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
       <c r="O5" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="1">
+        <v>5</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="1">
-        <v>1</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="1"/>
+      <c r="G6" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
+      <c r="H6" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="I6" s="2" t="s">
         <v>49</v>
       </c>
       <c r="J6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L6" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
+      <c r="M6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="O6" s="2" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C7" s="1">
         <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L7" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
       <c r="O7" s="2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="C8" s="1">
         <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>64</v>
@@ -1308,147 +1414,135 @@
       <c r="L8" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="M8" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>67</v>
-      </c>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
       <c r="O8" s="2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" s="1">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C9" s="1">
-        <v>2</v>
-      </c>
-      <c r="D9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="J9" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>22</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>42</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
       <c r="O9" s="2" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C10" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F10" s="1"/>
-      <c r="G10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>42</v>
-      </c>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
       <c r="I10" s="2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>22</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C11" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="J11" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="H11" s="1"/>
-      <c r="I11" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="K11" s="2" t="s">
         <v>22</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
@@ -1459,7 +1553,7 @@
         <v>88</v>
       </c>
       <c r="C12" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>89</v>
@@ -1469,13 +1563,13 @@
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>88</v>
@@ -1487,119 +1581,125 @@
         <v>91</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>42</v>
+        <v>92</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C13" s="1">
         <v>1</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="2" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>22</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
+        <v>99</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>100</v>
+      </c>
       <c r="O13" s="2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C14" s="1">
         <v>1</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="H14" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H14" s="1"/>
+      <c r="I14" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="J14" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="I14" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>103</v>
-      </c>
       <c r="K14" s="2" t="s">
         <v>22</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
       <c r="O14" s="2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C15" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E15" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F15" s="1"/>
+      <c r="G15" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="J15" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>110</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>22</v>
@@ -1607,10 +1707,14 @@
       <c r="L15" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
+      <c r="M15" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="O15" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
@@ -1621,95 +1725,107 @@
         <v>113</v>
       </c>
       <c r="C16" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>114</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
+      <c r="G16" s="2" t="s">
+        <v>116</v>
+      </c>
       <c r="H16" s="1"/>
       <c r="I16" s="2" t="s">
-        <v>115</v>
+        <v>63</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>22</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
       <c r="O16" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C17" s="1">
+        <v>4</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C17" s="1">
-        <v>3</v>
-      </c>
-      <c r="D17" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>108</v>
-      </c>
       <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
+      <c r="G17" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="I17" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L17" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="J17" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
+      <c r="M17" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="O17" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C18" s="1">
         <v>1</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F18" s="1"/>
+      <c r="G18" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="F18" s="2" t="s">
+      <c r="H18" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
       <c r="I18" s="2" t="s">
-        <v>109</v>
+        <v>63</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>128</v>
@@ -1723,7 +1839,7 @@
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
       <c r="O18" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
@@ -1734,28 +1850,28 @@
         <v>131</v>
       </c>
       <c r="C19" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>132</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="2" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>22</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
@@ -1765,76 +1881,68 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C20" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>138</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="2" t="s">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>22</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="N20" s="2" t="s">
-        <v>141</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
       <c r="O20" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C21" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="F21" s="1"/>
-      <c r="G21" s="2" t="s">
-        <v>146</v>
-      </c>
+      <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="J21" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="J21" s="2" t="s">
-        <v>143</v>
-      </c>
       <c r="K21" s="2" t="s">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>148</v>
@@ -1859,16 +1967,18 @@
         <v>151</v>
       </c>
       <c r="E22" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F22" s="1"/>
+      <c r="G22" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="J22" s="2" t="s">
         <v>153</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>150</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>22</v>
@@ -1876,94 +1986,90 @@
       <c r="L22" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="M22" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>155</v>
-      </c>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
       <c r="O22" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>156</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>157</v>
       </c>
       <c r="C23" s="1">
         <v>1</v>
       </c>
       <c r="D23" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F23" s="1"/>
+      <c r="G23" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L23" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="J23" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="N23" s="2" t="s">
-        <v>162</v>
-      </c>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
       <c r="O23" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C24" s="1">
+        <v>1</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="E24" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C24" s="1">
-        <v>2</v>
-      </c>
-      <c r="D24" s="2" t="s">
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="J24" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="K24" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L24" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="F24" s="1"/>
-      <c r="G24" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L24" s="2" t="s">
+      <c r="M24" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="N24" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
       <c r="O24" s="2" t="s">
         <v>24</v>
       </c>
@@ -1982,16 +2088,18 @@
         <v>170</v>
       </c>
       <c r="E25" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="J25" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>169</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>22</v>
@@ -2019,31 +2127,267 @@
         <v>176</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>177</v>
+        <v>133</v>
       </c>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L26" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="J26" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L26" s="2" t="s">
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="M26" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="N26" s="2" t="s">
+      <c r="B27" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="O26" s="2" t="s">
-        <v>52</v>
+      <c r="C27" s="1">
+        <v>1</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F27" s="1"/>
+      <c r="G27" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="H27" s="1"/>
+      <c r="I27" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C28" s="1">
+        <v>1</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C29" s="1">
+        <v>1</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="O29" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C30" s="1">
+        <v>1</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C31" s="1">
+        <v>2</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F31" s="1"/>
+      <c r="G31" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C32" s="1">
+        <v>1</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="N32" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="O32" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/Generate Files/BOM/243-436_PCB-Support-STM32F407.xlsx
+++ b/Generate Files/BOM/243-436_PCB-Support-STM32F407.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lecegeplimoilou-my.sharepoint.com/personal/kevin_cotton_cegeplimoilou_ca/Documents/_Cours-TGE/243-436-Dev-Prod4-Certifications/laboratoires/Labo1-Kit-Developpement-STM32/243-436-PCB-Support-STM32F407/Generate Files/BOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E556556E-FEDB-4E74-A729-C2F99570CC24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4785766C-DEEF-4405-A4CA-9CD24D3A443C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8880" xr2:uid="{898CD67B-8DE6-472D-ACF8-2736EC8F45DD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{70CBCBFD-1FBA-45C6-825C-CDE4DBF0641D}"/>
   </bookViews>
   <sheets>
     <sheet name="243-436_PCB-Support-STM32F407" sheetId="1" r:id="rId1"/>
@@ -1085,7 +1085,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED8784F8-9DF7-4BCD-8ABB-BCA9217864F8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1A17B6D-D7B4-415C-B61D-4F9E9DD390CA}">
   <dimension ref="A1:O32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
